--- a/public/exports/29189374.xlsx
+++ b/public/exports/29189374.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461926</t>
+          <t xml:space="preserve">311461967</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">EWII Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -10714,7 +10714,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539849</t>
+          <t xml:space="preserve">311539909</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539849</t>
+          <t xml:space="preserve">311539909</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539849</t>
+          <t xml:space="preserve">311539909</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10939,7 +10939,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539849</t>
+          <t xml:space="preserve">311539909</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539849</t>
+          <t xml:space="preserve">311539909</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11089,7 +11089,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539849</t>
+          <t xml:space="preserve">311539909</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">

--- a/public/exports/29189374.xlsx
+++ b/public/exports/29189374.xlsx
@@ -4639,12 +4639,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461967</t>
+          <t xml:space="preserve">311461926</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EWII Energi A/S</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -10714,7 +10714,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10939,7 +10939,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11089,7 +11089,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539909</t>
+          <t xml:space="preserve">311539849</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
